--- a/transport-mode/transport-mode.xlsx
+++ b/transport-mode/transport-mode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3B11E8-9877-4033-A576-1A0FFA05F08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F584A1-A10A-4BE9-8523-9989567B1DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vocabulary" sheetId="2" r:id="rId1"/>
@@ -113,9 +113,6 @@
     <t>dct:publisher</t>
   </si>
   <si>
-    <t>NAPCORE SubWG4.4</t>
-  </si>
-  <si>
     <t>dct:contributor</t>
   </si>
   <si>
@@ -176,9 +173,6 @@
     <t>owl:deprecated^^xsd:boolean</t>
   </si>
   <si>
-    <t>dcterms:replacedBy</t>
-  </si>
-  <si>
     <t>Road transport</t>
   </si>
   <si>
@@ -258,9 +252,6 @@
   </si>
   <si>
     <t>https://w3id.org/mobilitydcat-ap/transport-mode/tram-light-rail</t>
-  </si>
-  <si>
-    <t>Tram and light rail</t>
   </si>
   <si>
     <t>Street‑level rail vehicle operating in mixed traffic or dedicated lanes</t>
@@ -1370,10 +1361,19 @@
     <t>ShuttleService</t>
   </si>
   <si>
-    <t>Draft Controlled Vocabulary</t>
-  </si>
-  <si>
     <t>skos:narrower</t>
+  </si>
+  <si>
+    <t>dcterms:isReplacedBy</t>
+  </si>
+  <si>
+    <t>NAPCORE Task 4.4</t>
+  </si>
+  <si>
+    <t>Published Controlled Vocabulary</t>
+  </si>
+  <si>
+    <t>Tram, Light rail</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1539,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1632,6 +1632,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1954,7 +1955,7 @@
   <dimension ref="A1:H58"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="65" customWidth="1"/>
+    <col min="1" max="1" width="63.42578125" customWidth="1"/>
     <col min="2" max="2" width="60.28515625" customWidth="1"/>
     <col min="3" max="3" width="85.28515625" style="6" customWidth="1"/>
     <col min="4" max="5" width="71.85546875" style="1" customWidth="1"/>
@@ -2009,16 +2010,16 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="27"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -2027,52 +2028,52 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>390</v>
       </c>
       <c r="C8" s="27"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="27"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="27"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" s="27"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="44" t="s">
         <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
       </c>
       <c r="C12" s="27"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="str">
         <f>_xlfn.CONCAT(B1,"/",B12)</f>
@@ -2082,25 +2083,25 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="C14" s="27"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C15" s="27"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>391</v>
@@ -2108,28 +2109,28 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="C19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>31</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -2138,10 +2139,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D20" s="37" t="str">
         <f>_xlfn.TEXTJOIN(",",,A21:A25)</f>
@@ -2154,14 +2155,14 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
-        <f t="shared" ref="A21:A28" si="1">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B21)," ","-"),",",""))</f>
+        <f t="shared" ref="A21:A29" si="1">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B21)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21"/>
       <c r="E21" t="str">
@@ -2175,10 +2176,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/motorcycle</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D22"/>
       <c r="E22" t="str">
@@ -2192,10 +2193,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bus</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D23"/>
       <c r="E23" t="str">
@@ -2209,10 +2210,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/coach</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E24" s="14" t="str">
         <f>A20</f>
@@ -2226,10 +2227,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/truck</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D25"/>
       <c r="E25" t="str">
@@ -2243,10 +2244,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D26" s="15" t="str">
         <f>_xlfn.TEXTJOIN(",",,A27:A29,A31)</f>
@@ -2261,10 +2262,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/long-distance-rail</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E27" s="1" t="str">
         <f>A26</f>
@@ -2277,10 +2278,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/regional-and-local-rail</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="str">
@@ -2291,13 +2292,13 @@
     </row>
     <row r="29" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>59</v>
+        <v>392</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D29" s="31"/>
       <c r="E29" s="31" t="str">
@@ -2312,7 +2313,7 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/metro-subway-train</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="16"/>
@@ -2332,10 +2333,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/metro</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="15" t="str">
@@ -2350,10 +2351,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D32" s="15" t="str">
         <f>_xlfn.TEXTJOIN(",",,A33:A36)</f>
@@ -2368,10 +2369,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/maritime</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E33" s="1" t="str">
         <f>A32</f>
@@ -2384,10 +2385,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/inland-waterways</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E34" s="1" t="str">
         <f>A32</f>
@@ -2400,10 +2401,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/shuttle-ferry</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E35" s="1" t="str">
         <f>A32</f>
@@ -2416,10 +2417,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-taxi</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D36" s="15"/>
       <c r="E36" s="15" t="str">
@@ -2434,10 +2435,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D37" s="15" t="str">
         <f>_xlfn.TEXTJOIN(",",,A39:A40)</f>
@@ -2452,10 +2453,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
@@ -2474,10 +2475,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/aeroplane</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E39" s="1" t="str">
         <f>A37</f>
@@ -2490,25 +2491,25 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-taxi</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E40" s="1" t="str">
         <f>A37</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="14" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A41" s="28" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D41" s="15" t="str">
         <f>_xlfn.TEXTJOIN(",",,A42:A45)</f>
@@ -2523,10 +2524,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/cableways</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D42"/>
       <c r="E42" t="str">
@@ -2536,13 +2537,13 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E43" s="1" t="str">
         <f>A41</f>
@@ -2551,13 +2552,13 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E44" s="1" t="str">
         <f>A41</f>
@@ -2570,10 +2571,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/seasonal-transport</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="15" t="str">
@@ -2588,10 +2589,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/micromobility</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D46" s="15" t="str">
         <f>_xlfn.TEXTJOIN(",",,A47:A49)</f>
@@ -2602,13 +2603,13 @@
     </row>
     <row r="47" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B47" s="42" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E47" s="1" t="str">
         <f>A46</f>
@@ -2621,10 +2622,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/e-scooter</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D48" s="15"/>
       <c r="E48" s="15" t="str">
@@ -2639,10 +2640,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/moped</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="15" t="str">
@@ -2657,10 +2658,10 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/pedestrian</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D50" s="31"/>
       <c r="E50" s="31"/>
@@ -2672,7 +2673,7 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/other</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -2681,7 +2682,7 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bike-hire</v>
       </c>
       <c r="B52" s="43" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="16"/>
@@ -2701,7 +2702,7 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bike-sharing</v>
       </c>
       <c r="B53" s="43" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="16"/>
@@ -2721,7 +2722,7 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car-hire</v>
       </c>
       <c r="B54" s="43" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="16"/>
@@ -2741,7 +2742,7 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car-pooling</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="16"/>
@@ -2761,7 +2762,7 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car-sharing</v>
       </c>
       <c r="B56" s="43" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="16"/>
@@ -2781,7 +2782,7 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/ride-pooling</v>
       </c>
       <c r="B57" s="43" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="16"/>
@@ -2801,7 +2802,7 @@
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/taxi</v>
       </c>
       <c r="B58" s="43" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="16"/>
@@ -2837,295 +2838,295 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C25" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C26" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -3140,90 +3141,90 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3240,91 +3241,91 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C52" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D55" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D61" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -3345,7 +3346,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="22"/>
@@ -3354,10 +3355,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
@@ -3365,10 +3366,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -3376,10 +3377,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
@@ -3387,10 +3388,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
@@ -3398,10 +3399,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="21"/>
@@ -3409,10 +3410,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
@@ -3420,10 +3421,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
@@ -3431,10 +3432,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="21"/>
@@ -3449,7 +3450,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -3458,104 +3459,104 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>223</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="E16" s="21" t="s">
         <v>236</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>240</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3567,7 +3568,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -3576,26 +3577,26 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
@@ -3609,7 +3610,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -3618,121 +3619,121 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="D26" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>257</v>
-      </c>
       <c r="E26" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3744,7 +3745,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -3753,7 +3754,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C33" s="21"/>
       <c r="D33" s="23"/>
@@ -3761,7 +3762,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="23"/>
@@ -3769,7 +3770,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="23"/>
@@ -3777,7 +3778,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C36" s="21"/>
       <c r="D36" s="23"/>
@@ -3785,7 +3786,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C37" s="21"/>
       <c r="D37" s="23"/>
@@ -3793,7 +3794,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C38" s="21"/>
       <c r="D38" s="23"/>
@@ -3801,7 +3802,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C39" s="21"/>
       <c r="D39" s="23"/>
@@ -3809,7 +3810,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C40" s="21"/>
       <c r="D40" s="23"/>
@@ -3824,10 +3825,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C42" s="21"/>
       <c r="D42" s="21"/>
@@ -3835,70 +3836,70 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="D43" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="E43" s="23" t="s">
         <v>271</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B44" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="E44" s="23" t="s">
         <v>275</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B45" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="E45" s="23" t="s">
         <v>279</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3910,10 +3911,10 @@
     </row>
     <row r="48" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="21"/>
@@ -3921,104 +3922,104 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -4030,10 +4031,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
@@ -4041,53 +4042,53 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B57" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="E57" s="23" t="s">
         <v>303</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="21" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -4099,10 +4100,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C61" s="22"/>
       <c r="D61" s="21"/>
@@ -4110,36 +4111,36 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="D62" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="E62" s="23" t="s">
         <v>313</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="D62" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="E62" s="23" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B63" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="E63" s="23" t="s">
         <v>317</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="E63" s="23" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -4151,10 +4152,10 @@
     </row>
     <row r="65" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A65" s="24" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C65" s="22"/>
       <c r="D65" s="21"/>
@@ -4162,121 +4163,121 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="D66" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="B66" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="C66" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>326</v>
-      </c>
       <c r="E66" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="D67" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="B67" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="C67" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>330</v>
-      </c>
       <c r="E67" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="D68" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="B68" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="C68" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>334</v>
-      </c>
       <c r="E68" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="D69" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="B69" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>338</v>
-      </c>
       <c r="E69" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="21" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="D71" s="23" t="s">
         <v>342</v>
       </c>
-      <c r="B71" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="C71" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>345</v>
-      </c>
       <c r="E71" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="21" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -4288,10 +4289,10 @@
     </row>
     <row r="74" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A74" s="24" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C74" s="21"/>
       <c r="D74" s="23"/>
@@ -4299,10 +4300,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C75" s="21"/>
       <c r="D75" s="23"/>
@@ -4310,10 +4311,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C76" s="21"/>
       <c r="D76" s="23"/>
@@ -4321,10 +4322,10 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="21" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C77" s="21"/>
       <c r="D77" s="23"/>
@@ -4339,10 +4340,10 @@
     </row>
     <row r="79" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A79" s="24" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C79" s="22"/>
       <c r="D79" s="21"/>
@@ -4350,172 +4351,172 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="21" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B80" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="D80" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="E80" s="23" t="s">
         <v>356</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="D80" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="E80" s="23" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E81" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="21" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B83" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="D83" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="E83" s="23" t="s">
         <v>366</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="D83" s="23" t="s">
-        <v>368</v>
-      </c>
-      <c r="E83" s="23" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="21" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="21" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B85" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D85" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="E85" s="23" t="s">
         <v>373</v>
-      </c>
-      <c r="C85" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="D85" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="E85" s="23" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="21" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E86" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="21" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B87" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="D87" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="E87" s="23" t="s">
         <v>380</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>381</v>
-      </c>
-      <c r="D87" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="E87" s="23" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="21" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="D89" s="23" t="s">
         <v>387</v>
       </c>
-      <c r="B89" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="D89" s="23" t="s">
-        <v>390</v>
-      </c>
       <c r="E89" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4546,12 +4547,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4756,20 +4759,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E07F1C-30C1-44FD-9041-9A393B69CD1A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
+    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4794,12 +4798,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E07F1C-30C1-44FD-9041-9A393B69CD1A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
-    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>